--- a/claims_dashboard.xlsx
+++ b/claims_dashboard.xlsx
@@ -273,7 +273,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Quarter</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -284,6 +300,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
@@ -371,7 +388,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Claim Status</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -382,8 +415,24 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Claim Count</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -460,6 +509,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -470,7 +520,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Month</a:t>
+                  <a:t>Report Month</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -486,6 +536,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
@@ -573,7 +624,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Injury Cause</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -584,8 +651,24 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Claim Count</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -656,7 +739,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Injury Body Part</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -667,8 +766,24 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Total Incurred Loss ($)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -24077,7 +24192,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Claims Analytics — Executive KPIs</t>
+          <t>Claims Analytics - Executive KPIs</t>
         </is>
       </c>
     </row>
@@ -24269,7 +24384,7 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>NOTE: Slicers (School Level / Department / Status) require a live PivotTable connected to the "Data" sheet's ClaimsData table — see dashboard_pivot_slicer_guide.txt for exact steps.</t>
+          <t>NOTE: Slicers (School Level / Department / Status) require a live PivotTable connected to the "Data" sheet's ClaimsData table - see dashboard_pivot_slicer_guide.txt for exact steps.</t>
         </is>
       </c>
     </row>

--- a/claims_dashboard.xlsx
+++ b/claims_dashboard.xlsx
@@ -19,13 +19,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="166" formatCode="$#,##0.00"/>
     <numFmt numFmtId="167" formatCode="$#,##0"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,6 +59,11 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="009C5700"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
@@ -69,8 +75,18 @@
       <b val="1"/>
       <color rgb="00375623"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -81,6 +97,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
         <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -110,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -122,12 +144,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -230,7 +259,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Claims: Prior vs Current Quarter</a:t>
+              <a:t>Claims Fell 44% After the Winter Peak (Q1-2025 -&gt; Q2-2025)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -245,7 +274,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Executive_KPIs'!B14</f>
+              <f>'Executive_KPIs'!B18</f>
             </strRef>
           </tx>
           <spPr>
@@ -255,12 +284,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Executive_KPIs'!$A$15:$A$16</f>
+              <f>'Executive_KPIs'!$A$19:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Executive_KPIs'!$B$15:$B$16</f>
+              <f>'Executive_KPIs'!$B$19:$B$20</f>
             </numRef>
           </val>
         </ser>
@@ -345,7 +374,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Claim Status Breakdown</a:t>
+              <a:t>51% of Claims Are Already Closed</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -360,7 +389,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Executive_KPIs'!I13</f>
+              <f>'Executive_KPIs'!I17</f>
             </strRef>
           </tx>
           <spPr>
@@ -370,12 +399,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Executive_KPIs'!$H$14:$H$16</f>
+              <f>'Executive_KPIs'!$H$18:$H$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Executive_KPIs'!$I$14:$I$16</f>
+              <f>'Executive_KPIs'!$I$18:$I$20</f>
             </numRef>
           </val>
         </ser>
@@ -460,7 +489,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Claims by Month (Winter Slip/Fall Spike)</a:t>
+              <a:t>Claims Spike Nov-Feb, Driven by Winter Slip/Fall</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -581,7 +610,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Top 10 Injury Causes</a:t>
+              <a:t>Slip/Fall Is the #1 Injury Cause (31% of All Claims)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -604,6 +633,105 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="5"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="6"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="8"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
               <f>'Trends'!$A$19:$A$27</f>
@@ -696,7 +824,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Total Incurred Loss by Body Part</a:t>
+              <a:t>Shoulder &amp; Wrist Injuries Drive the Highest Total Loss</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -719,6 +847,127 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="5"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="6"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="8"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="9"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="10"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
               <f>'Trends'!$A$31:$A$41</f>
@@ -798,16 +1047,301 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>4 Elementary Sites Drive 55% of Total Incurred Loss</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Trends'!B61</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="5"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="6"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A6A6A6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A6A6A6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="8"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="9"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <cat>
+            <numRef>
+              <f>'Trends'!$A$62:$A$71</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Trends'!$B$62:$B$71</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Trends'!C61</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Trends'!$C$62:$C$71</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="200"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>School Site</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Total Incurred Loss ($)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+        <crosses val="max"/>
+      </valAx>
+      <valAx>
+        <axId val="200"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Cumulative % of Total Loss</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>11</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4320000" cy="2520000"/>
+    <ext cx="4680000" cy="2700000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -826,10 +1360,10 @@
     <from>
       <col>11</col>
       <colOff>0</colOff>
-      <row>11</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4320000" cy="2520000"/>
+    <ext cx="4680000" cy="2700000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -915,6 +1449,28 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>59</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -987,14 +1543,27 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="DrilldownData" displayName="DrilldownData" ref="A3:E267" headerRowCount="1">
-  <autoFilter ref="A3:E267"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="SiteLossPareto" displayName="SiteLossPareto" ref="A61:C71" headerRowCount="1">
+  <autoFilter ref="A61:C71"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="SchoolSite"/>
+    <tableColumn id="2" name="TotalIncurredLoss"/>
+    <tableColumn id="3" name="CumulativePct"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="DrilldownData" displayName="DrilldownData" ref="A4:F268" headerRowCount="1">
+  <autoFilter ref="A4:F268"/>
+  <tableColumns count="6">
     <tableColumn id="1" name="SchoolSite"/>
     <tableColumn id="2" name="Department"/>
     <tableColumn id="3" name="InjuryCause"/>
     <tableColumn id="4" name="ClaimCount"/>
     <tableColumn id="5" name="IncurredLoss"/>
+    <tableColumn id="6" name="PendingEstimateClaims"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -24171,7 +24740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -24272,7 +24841,7 @@
       <c r="B9" s="7" t="n"/>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>$1,516,882</t>
+          <t>$1.52M</t>
         </is>
       </c>
       <c r="E9" s="7" t="n"/>
@@ -24284,113 +24853,137 @@
       <c r="H9" s="7" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Pending Loss Estimate</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>6 claims</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Claims by Quarter (Last 2 Complete Quarters)</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>Status Breakdown</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>(Q3-2025 excluded: only July is in range, so it's a partial quarter, not a real decline)</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n"/>
-      <c r="H13" t="inlineStr">
+      <c r="B17" s="1" t="n"/>
+      <c r="H17" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>Quarter</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>Claim Count</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I18" t="n">
         <v>140</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Q1-2025</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B19" t="n">
         <v>118</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="I19" t="n">
         <v>192</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Q2-2025</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B20" t="n">
         <v>66</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Re-opened</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I20" t="n">
         <v>43</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>% Change</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>-44.1%</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>DATA QUALITY: 400 raw records -&gt; 15 exact duplicates removed -&gt; 3 missing IDs retained as UNASSIGNED-### -&gt; 10 exceptions quarantined -&gt; 375 clean records, of which 6 are pending a loss estimate (blank reserve, not zero). Full audit trail: claims_cleaning_log.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>NOTE: Slicers (School Level / Department / Status) require a live PivotTable connected to the "Data" sheet's ClaimsData table - see dashboard_pivot_slicer_guide.txt for exact steps.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A22:I22"/>
+  <mergeCells count="2">
+    <mergeCell ref="A33:M33"/>
+    <mergeCell ref="A35:M35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -24403,7 +24996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -24678,7 +25271,7 @@
           <t>Shoulder</t>
         </is>
       </c>
-      <c r="B31" s="12" t="n">
+      <c r="B31" s="14" t="n">
         <v>275674.01</v>
       </c>
     </row>
@@ -24688,7 +25281,7 @@
           <t>Wrist</t>
         </is>
       </c>
-      <c r="B32" s="12" t="n">
+      <c r="B32" s="14" t="n">
         <v>232301.36</v>
       </c>
     </row>
@@ -24698,7 +25291,7 @@
           <t>Back</t>
         </is>
       </c>
-      <c r="B33" s="12" t="n">
+      <c r="B33" s="14" t="n">
         <v>222632.15</v>
       </c>
     </row>
@@ -24708,7 +25301,7 @@
           <t>Ankle</t>
         </is>
       </c>
-      <c r="B34" s="12" t="n">
+      <c r="B34" s="14" t="n">
         <v>221795.79</v>
       </c>
     </row>
@@ -24718,7 +25311,7 @@
           <t>Knee</t>
         </is>
       </c>
-      <c r="B35" s="12" t="n">
+      <c r="B35" s="14" t="n">
         <v>181100.15</v>
       </c>
     </row>
@@ -24728,7 +25321,7 @@
           <t>Head</t>
         </is>
       </c>
-      <c r="B36" s="12" t="n">
+      <c r="B36" s="14" t="n">
         <v>86371.92</v>
       </c>
     </row>
@@ -24738,7 +25331,7 @@
           <t>Multiple/Other</t>
         </is>
       </c>
-      <c r="B37" s="12" t="n">
+      <c r="B37" s="14" t="n">
         <v>72004.3</v>
       </c>
     </row>
@@ -24748,7 +25341,7 @@
           <t>Finger</t>
         </is>
       </c>
-      <c r="B38" s="12" t="n">
+      <c r="B38" s="14" t="n">
         <v>69755.3</v>
       </c>
     </row>
@@ -24758,7 +25351,7 @@
           <t>Hand</t>
         </is>
       </c>
-      <c r="B39" s="12" t="n">
+      <c r="B39" s="14" t="n">
         <v>59959.49</v>
       </c>
     </row>
@@ -24768,7 +25361,7 @@
           <t>Neck</t>
         </is>
       </c>
-      <c r="B40" s="12" t="n">
+      <c r="B40" s="14" t="n">
         <v>58359.99</v>
       </c>
     </row>
@@ -24778,12 +25371,12 @@
           <t>Foot</t>
         </is>
       </c>
-      <c r="B41" s="12" t="n">
+      <c r="B41" s="14" t="n">
         <v>36927.48</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>Claims by Month x School Level</t>
         </is>
@@ -25001,6 +25594,160 @@
       </c>
       <c r="D57" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>4 Elementary Sites Drive 55% of Total Incurred Loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>SchoolSite</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="inlineStr">
+        <is>
+          <t>TotalIncurredLoss</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>CumulativePct</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Blue Spruce Elementary School</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="n">
+        <v>249306.76</v>
+      </c>
+      <c r="C62" s="15" t="n">
+        <v>0.1643547552553761</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Timber Trail Elementary School</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="n">
+        <v>241682.49</v>
+      </c>
+      <c r="C63" s="15" t="n">
+        <v>0.3236832327240972</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Willow Creek Elementary School</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="n">
+        <v>195193.61</v>
+      </c>
+      <c r="C64" s="15" t="n">
+        <v>0.4523640514831366</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Sunrise Elementary School</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="n">
+        <v>152099.55</v>
+      </c>
+      <c r="C65" s="15" t="n">
+        <v>0.5526352367277839</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Cedar Ridge High School</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="n">
+        <v>131428.37</v>
+      </c>
+      <c r="C66" s="15" t="n">
+        <v>0.6392790067762295</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Vivekananda International Academy</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="n">
+        <v>130400.27</v>
+      </c>
+      <c r="C67" s="15" t="n">
+        <v>0.7252450048947119</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Meadowbrook Middle School</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="n">
+        <v>124625.71</v>
+      </c>
+      <c r="C68" s="15" t="n">
+        <v>0.8074041411555075</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Aspen Grove Middle School</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="n">
+        <v>106695.29</v>
+      </c>
+      <c r="C69" s="15" t="n">
+        <v>0.8777427002657834</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Prairie View High School</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="n">
+        <v>103261.22</v>
+      </c>
+      <c r="C70" s="15" t="n">
+        <v>0.9458173587326119</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Foothills High School</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="n">
+        <v>82188.67</v>
+      </c>
+      <c r="C71" s="15" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -25016,11 +25763,12 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  <tableParts count="4">
+  <tableParts count="5">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>
@@ -25031,14 +25779,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E267"/>
+  <dimension ref="A1:F268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25048,54 +25797,43 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>"Pending" = incurred loss not yet known (blank reserve), not zero cost. See PendingEstimateClaims column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>SchoolSite</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>InjuryCause</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>ClaimCount</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>IncurredLoss</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Aspen Grove Middle School</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Administration</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Struck By/Against</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" s="12" t="n">
-        <v>12217.54</v>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>PendingEstimateClaims</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -25111,14 +25849,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Repetitive Motion</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="12" t="n">
-        <v>3453.29</v>
+        <v>3</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>12217.54</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -25134,14 +25875,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Repetitive Motion</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="12" t="n">
-        <v>3111.31</v>
+      <c r="E6" s="14" t="n">
+        <v>3453.29</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -25152,19 +25896,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>6365.83</v>
+        <v>1</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>3111.31</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -25180,14 +25927,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="12" t="n">
-        <v>1095.53</v>
+        <v>2</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>6365.83</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -25198,19 +25948,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Classroom/Instruction</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vehicle Accident</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="12" t="n">
-        <v>6448.21</v>
+      <c r="E9" s="14" t="n">
+        <v>1095.53</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -25226,14 +25979,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Vehicle Accident</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="12" t="n">
-        <v>4940.14</v>
+      <c r="E10" s="14" t="n">
+        <v>6448.21</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -25249,14 +26005,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lifting</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="12" t="n">
-        <v>4240.34</v>
+      <c r="E11" s="14" t="n">
+        <v>4940.14</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -25272,14 +26031,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Burn</t>
+          <t>Lifting</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>4118.91</v>
+        <v>1</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>4240.34</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -25295,14 +26057,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Burn</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>3847</v>
+        <v>2</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>4118.91</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -25318,14 +26083,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="12" t="n">
-        <v>1160.26</v>
+      <c r="E14" s="14" t="n">
+        <v>3847</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -25341,14 +26109,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="12" t="n">
-        <v>800.89</v>
+      <c r="E15" s="14" t="n">
+        <v>1160.26</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -25359,7 +26130,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Custodial</t>
+          <t>Classroom/Instruction</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -25370,8 +26141,11 @@
       <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="12" t="n">
-        <v>1306.38</v>
+      <c r="E16" s="14" t="n">
+        <v>800.89</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -25382,19 +26156,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>Custodial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lifting</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
-      </c>
-      <c r="E17" s="12" t="n">
-        <v>31474.46</v>
+        <v>1</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>1306.38</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -25410,14 +26187,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Lifting</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" s="12" t="n">
-        <v>3433.98</v>
+        <v>7</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>31474.46</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -25428,19 +26208,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Grounds</t>
+          <t>Facilities</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lifting</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="12" t="n">
-        <v>4603.79</v>
+        <v>2</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>3433.98</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -25456,14 +26239,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Repetitive Motion</t>
+          <t>Lifting</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="12" t="n">
-        <v>3302.2</v>
+      <c r="E20" s="14" t="n">
+        <v>4603.79</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -25479,14 +26265,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Repetitive Motion</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="12" t="n">
-        <v>2186.87</v>
+      <c r="E21" s="14" t="n">
+        <v>3302.2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -25502,14 +26291,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" s="12" t="n">
-        <v>1535.15</v>
+        <v>1</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>2186.87</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -25525,14 +26317,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>1414.76</v>
+        <v>2</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>1535.15</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -25543,7 +26338,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Grounds</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -25554,8 +26349,11 @@
       <c r="D24" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="12" t="n">
-        <v>2903.5</v>
+      <c r="E24" s="14" t="n">
+        <v>1414.76</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -25571,14 +26369,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="12" t="n">
-        <v>1398.38</v>
+      <c r="E25" s="14" t="n">
+        <v>2903.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -25594,37 +26395,43 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Repetitive Motion</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>1</v>
       </c>
-      <c r="E26" s="12" t="n">
-        <v>1336.57</v>
+      <c r="E26" s="14" t="n">
+        <v>1398.38</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Blue Spruce Elementary School</t>
+          <t>Aspen Grove Middle School</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Repetitive Motion</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
-      </c>
-      <c r="E27" s="12" t="n">
-        <v>19611.75</v>
+        <v>1</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>1336.57</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -25640,14 +26447,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Student Assault</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="12" t="n">
-        <v>4437.81</v>
+        <v>4</v>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>19611.75</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -25663,14 +26473,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Student Assault</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" s="12" t="n">
-        <v>3067.31</v>
+        <v>1</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>4437.81</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -25681,19 +26494,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="12" t="n">
-        <v>2159.57</v>
+        <v>2</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>3067.31</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -25709,14 +26525,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>1</v>
       </c>
-      <c r="E31" s="12" t="n">
-        <v>2081.93</v>
+      <c r="E31" s="14" t="n">
+        <v>2159.57</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -25727,19 +26546,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Classroom/Instruction</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
-      </c>
-      <c r="E32" s="12" t="n">
-        <v>41536.78</v>
+        <v>1</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>2081.93</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -25755,14 +26577,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Vehicle Accident</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="12" t="n">
-        <v>7057.44</v>
+        <v>5</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>41536.78</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -25778,14 +26603,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Repetitive Motion</t>
+          <t>Vehicle Accident</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>1</v>
       </c>
-      <c r="E34" s="12" t="n">
-        <v>4355.63</v>
+      <c r="E34" s="14" t="n">
+        <v>7057.44</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -25801,14 +26629,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Student Assault</t>
+          <t>Repetitive Motion</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>1</v>
       </c>
-      <c r="E35" s="12" t="n">
-        <v>3336</v>
+      <c r="E35" s="14" t="n">
+        <v>4355.63</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -25824,14 +26655,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Student Assault</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
-      </c>
-      <c r="E36" s="12" t="n">
-        <v>2197.57</v>
+        <v>1</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>3336</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -25847,14 +26681,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="12" t="n">
-        <v>849.63</v>
+        <v>2</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>2197.57</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -25865,19 +26702,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Custodial</t>
+          <t>Classroom/Instruction</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
-      </c>
-      <c r="E38" s="12" t="n">
-        <v>22308.65</v>
+        <v>1</v>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>849.63</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -25893,14 +26733,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lifting</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="12" t="n">
-        <v>9508.440000000001</v>
+        <v>3</v>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>22308.65</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -25916,14 +26759,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Student Assault</t>
+          <t>Lifting</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>1</v>
       </c>
-      <c r="E40" s="12" t="n">
-        <v>4673.17</v>
+      <c r="E40" s="14" t="n">
+        <v>9508.440000000001</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -25939,14 +26785,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Student Assault</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>1</v>
       </c>
-      <c r="E41" s="12" t="n">
-        <v>1990.28</v>
+      <c r="E41" s="14" t="n">
+        <v>4673.17</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -25957,19 +26806,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>Custodial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
-      </c>
-      <c r="E42" s="12" t="n">
-        <v>16385.51</v>
+        <v>1</v>
+      </c>
+      <c r="E42" s="14" t="n">
+        <v>1990.28</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -25985,14 +26837,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Student Assault</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="12" t="n">
-        <v>8685.280000000001</v>
+        <v>4</v>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>16385.51</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -26008,14 +26863,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Repetitive Motion</t>
+          <t>Student Assault</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
-      </c>
-      <c r="E44" s="12" t="n">
-        <v>3785.94</v>
+        <v>1</v>
+      </c>
+      <c r="E44" s="14" t="n">
+        <v>8685.280000000001</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -26031,14 +26889,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Repetitive Motion</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="12" t="n">
-        <v>2898.16</v>
+        <v>2</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>3785.94</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -26049,19 +26910,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Food Service</t>
+          <t>Facilities</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E46" s="12" t="n">
-        <v>9899.389999999999</v>
+        <v>1</v>
+      </c>
+      <c r="E46" s="14" t="n">
+        <v>2898.16</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -26077,14 +26941,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" s="12" t="n">
-        <v>3864.06</v>
+        <v>2</v>
+      </c>
+      <c r="E47" s="14" t="n">
+        <v>9899.389999999999</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -26100,14 +26967,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Student Assault</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D48" t="n">
         <v>1</v>
       </c>
-      <c r="E48" s="12" t="n">
-        <v>3018.59</v>
+      <c r="E48" s="14" t="n">
+        <v>3864.06</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -26123,14 +26993,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Student Assault</t>
         </is>
       </c>
       <c r="D49" t="n">
         <v>1</v>
       </c>
-      <c r="E49" s="12" t="n">
-        <v>1720.16</v>
+      <c r="E49" s="14" t="n">
+        <v>3018.59</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -26146,14 +27019,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D50" t="n">
         <v>1</v>
       </c>
-      <c r="E50" s="12" t="n">
-        <v>756.79</v>
+      <c r="E50" s="14" t="n">
+        <v>1720.16</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -26164,19 +27040,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Grounds</t>
+          <t>Food Service</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lifting</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
-      </c>
-      <c r="E51" s="12" t="n">
-        <v>9821.32</v>
+        <v>1</v>
+      </c>
+      <c r="E51" s="14" t="n">
+        <v>756.79</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -26192,14 +27071,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Vehicle Accident</t>
+          <t>Lifting</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="12" t="n">
-        <v>8899.799999999999</v>
+        <v>2</v>
+      </c>
+      <c r="E52" s="14" t="n">
+        <v>9821.32</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -26215,14 +27097,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Vehicle Accident</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
-      </c>
-      <c r="E53" s="12" t="n">
-        <v>6114.51</v>
+        <v>1</v>
+      </c>
+      <c r="E53" s="14" t="n">
+        <v>8899.799999999999</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -26238,14 +27123,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Student Assault</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D54" t="n">
         <v>2</v>
       </c>
-      <c r="E54" s="12" t="n">
-        <v>3823.53</v>
+      <c r="E54" s="14" t="n">
+        <v>6114.51</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -26261,14 +27149,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Student Assault</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
-      </c>
-      <c r="E55" s="12" t="n">
-        <v>2822.53</v>
+        <v>2</v>
+      </c>
+      <c r="E55" s="14" t="n">
+        <v>3823.53</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -26284,14 +27175,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" s="12" t="n">
-        <v>1451.36</v>
+        <v>3</v>
+      </c>
+      <c r="E56" s="14" t="n">
+        <v>2822.53</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -26302,19 +27196,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Grounds</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
-      </c>
-      <c r="E57" s="12" t="n">
-        <v>17432.68</v>
+        <v>1</v>
+      </c>
+      <c r="E57" s="14" t="n">
+        <v>1451.36</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -26330,14 +27227,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Student Assault</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" s="12" t="n">
-        <v>8105</v>
+        <v>3</v>
+      </c>
+      <c r="E58" s="14" t="n">
+        <v>17432.68</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -26353,14 +27253,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Repetitive Motion</t>
+          <t>Student Assault</t>
         </is>
       </c>
       <c r="D59" t="n">
         <v>1</v>
       </c>
-      <c r="E59" s="12" t="n">
-        <v>5866.66</v>
+      <c r="E59" s="14" t="n">
+        <v>8105</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -26376,14 +27279,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Vehicle Accident</t>
+          <t>Repetitive Motion</t>
         </is>
       </c>
       <c r="D60" t="n">
         <v>1</v>
       </c>
-      <c r="E60" s="12" t="n">
-        <v>3910.43</v>
+      <c r="E60" s="14" t="n">
+        <v>5866.66</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -26399,37 +27305,43 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Vehicle Accident</t>
         </is>
       </c>
       <c r="D61" t="n">
         <v>1</v>
       </c>
-      <c r="E61" s="12" t="n">
-        <v>873.1</v>
+      <c r="E61" s="14" t="n">
+        <v>3910.43</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cedar Ridge High School</t>
+          <t>Blue Spruce Elementary School</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
-      </c>
-      <c r="E62" s="12" t="n">
-        <v>12406.2</v>
+        <v>1</v>
+      </c>
+      <c r="E62" s="14" t="n">
+        <v>873.1</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -26445,14 +27357,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Repetitive Motion</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" s="12" t="n">
-        <v>591.29</v>
+        <v>4</v>
+      </c>
+      <c r="E63" s="14" t="n">
+        <v>12406.2</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -26463,19 +27378,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Repetitive Motion</t>
         </is>
       </c>
       <c r="D64" t="n">
         <v>1</v>
       </c>
-      <c r="E64" s="12" t="n">
-        <v>21462</v>
+      <c r="E64" s="14" t="n">
+        <v>591.29</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -26491,14 +27409,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D65" t="n">
         <v>1</v>
       </c>
-      <c r="E65" s="12" t="n">
-        <v>2184.12</v>
+      <c r="E65" s="14" t="n">
+        <v>21462</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -26514,14 +27435,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D66" t="n">
         <v>1</v>
       </c>
-      <c r="E66" s="12" t="n">
-        <v>1112.54</v>
+      <c r="E66" s="14" t="n">
+        <v>2184.12</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -26532,19 +27456,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Classroom/Instruction</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D67" t="n">
         <v>1</v>
       </c>
-      <c r="E67" s="12" t="n">
-        <v>4353.78</v>
+      <c r="E67" s="14" t="n">
+        <v>1112.54</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -26555,19 +27482,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Custodial</t>
+          <t>Classroom/Instruction</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lifting</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D68" t="n">
         <v>1</v>
       </c>
-      <c r="E68" s="12" t="n">
-        <v>5315.71</v>
+      <c r="E68" s="14" t="n">
+        <v>4353.78</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -26583,14 +27513,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Repetitive Motion</t>
+          <t>Lifting</t>
         </is>
       </c>
       <c r="D69" t="n">
         <v>1</v>
       </c>
-      <c r="E69" s="12" t="n">
-        <v>3515.38</v>
+      <c r="E69" s="14" t="n">
+        <v>5315.71</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -26601,19 +27534,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>Custodial</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Vehicle Accident</t>
+          <t>Repetitive Motion</t>
         </is>
       </c>
       <c r="D70" t="n">
         <v>1</v>
       </c>
-      <c r="E70" s="12" t="n">
-        <v>12534.65</v>
+      <c r="E70" s="14" t="n">
+        <v>3515.38</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -26629,14 +27565,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lifting</t>
+          <t>Vehicle Accident</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
-      </c>
-      <c r="E71" s="12" t="n">
-        <v>8091.08</v>
+        <v>1</v>
+      </c>
+      <c r="E71" s="14" t="n">
+        <v>12534.65</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -26652,14 +27591,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Lifting</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" s="12" t="n">
-        <v>1709</v>
+        <v>2</v>
+      </c>
+      <c r="E72" s="14" t="n">
+        <v>8091.08</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -26670,19 +27612,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Food Service</t>
+          <t>Facilities</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Student Assault</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D73" t="n">
         <v>1</v>
       </c>
-      <c r="E73" s="12" t="n">
-        <v>6411.58</v>
+      <c r="E73" s="14" t="n">
+        <v>1709</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -26698,14 +27643,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Student Assault</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
-      </c>
-      <c r="E74" s="12" t="n">
-        <v>2280.5</v>
+        <v>1</v>
+      </c>
+      <c r="E74" s="14" t="n">
+        <v>6411.58</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -26716,19 +27664,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Grounds</t>
+          <t>Food Service</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D75" t="n">
         <v>2</v>
       </c>
-      <c r="E75" s="12" t="n">
-        <v>14496.08</v>
+      <c r="E75" s="14" t="n">
+        <v>2280.5</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -26744,14 +27695,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Student Assault</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
-      </c>
-      <c r="E76" s="12" t="n">
-        <v>7716.29</v>
+        <v>2</v>
+      </c>
+      <c r="E76" s="14" t="n">
+        <v>14496.08</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -26767,14 +27721,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Student Assault</t>
         </is>
       </c>
       <c r="D77" t="n">
         <v>1</v>
       </c>
-      <c r="E77" s="12" t="n">
-        <v>1571.52</v>
+      <c r="E77" s="14" t="n">
+        <v>7716.29</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -26785,19 +27742,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Grounds</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Vehicle Accident</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D78" t="n">
         <v>1</v>
       </c>
-      <c r="E78" s="12" t="n">
-        <v>9647.860000000001</v>
+      <c r="E78" s="14" t="n">
+        <v>1571.52</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -26813,14 +27773,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Vehicle Accident</t>
         </is>
       </c>
       <c r="D79" t="n">
         <v>1</v>
       </c>
-      <c r="E79" s="12" t="n">
-        <v>7461</v>
+      <c r="E79" s="14" t="n">
+        <v>9647.860000000001</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -26836,14 +27799,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Student Assault</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D80" t="n">
         <v>1</v>
       </c>
-      <c r="E80" s="12" t="n">
-        <v>6006.82</v>
+      <c r="E80" s="14" t="n">
+        <v>7461</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -26859,14 +27825,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Burn</t>
+          <t>Student Assault</t>
         </is>
       </c>
       <c r="D81" t="n">
         <v>1</v>
       </c>
-      <c r="E81" s="12" t="n">
-        <v>1958.12</v>
+      <c r="E81" s="14" t="n">
+        <v>6006.82</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -26882,14 +27851,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Burn</t>
         </is>
       </c>
       <c r="D82" t="n">
         <v>1</v>
       </c>
-      <c r="E82" s="12" t="n">
-        <v>602.85</v>
+      <c r="E82" s="14" t="n">
+        <v>1958.12</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -26905,37 +27877,45 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lifting</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D83" t="n">
         <v>1</v>
       </c>
-      <c r="E83" s="12" t="n">
+      <c r="E83" s="14" t="n">
+        <v>602.85</v>
+      </c>
+      <c r="F83" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Foothills High School</t>
+          <t>Cedar Ridge High School</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Burn</t>
+          <t>Lifting</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
-      </c>
-      <c r="E84" s="12" t="n">
-        <v>6614.29</v>
+        <v>1</v>
+      </c>
+      <c r="E84" s="17" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -26951,14 +27931,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Burn</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" s="12" t="n">
-        <v>929.4299999999999</v>
+        <v>2</v>
+      </c>
+      <c r="E85" s="14" t="n">
+        <v>6614.29</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -26969,19 +27952,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Student Assault</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D86" t="n">
         <v>1</v>
       </c>
-      <c r="E86" s="12" t="n">
-        <v>4158.57</v>
+      <c r="E86" s="14" t="n">
+        <v>929.4299999999999</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -26997,14 +27983,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Burn</t>
+          <t>Student Assault</t>
         </is>
       </c>
       <c r="D87" t="n">
         <v>1</v>
       </c>
-      <c r="E87" s="12" t="n">
-        <v>2048.06</v>
+      <c r="E87" s="14" t="n">
+        <v>4158.57</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -27020,14 +28009,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Burn</t>
         </is>
       </c>
       <c r="D88" t="n">
         <v>1</v>
       </c>
-      <c r="E88" s="12" t="n">
-        <v>1701</v>
+      <c r="E88" s="14" t="n">
+        <v>2048.06</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -27043,14 +28035,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D89" t="n">
         <v>1</v>
       </c>
-      <c r="E89" s="12" t="n">
-        <v>554.4299999999999</v>
+      <c r="E89" s="14" t="n">
+        <v>1701</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -27061,19 +28056,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Classroom/Instruction</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D90" t="n">
         <v>1</v>
       </c>
-      <c r="E90" s="12" t="n">
-        <v>4319.13</v>
+      <c r="E90" s="14" t="n">
+        <v>554.4299999999999</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -27089,14 +28087,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2</v>
-      </c>
-      <c r="E91" s="12" t="n">
-        <v>3492.46</v>
+        <v>1</v>
+      </c>
+      <c r="E91" s="14" t="n">
+        <v>4319.13</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -27112,14 +28113,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Burn</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" s="12" t="n">
-        <v>2146</v>
+        <v>2</v>
+      </c>
+      <c r="E92" s="14" t="n">
+        <v>3492.46</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -27130,19 +28134,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Custodial</t>
+          <t>Classroom/Instruction</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Burn</t>
         </is>
       </c>
       <c r="D93" t="n">
         <v>1</v>
       </c>
-      <c r="E93" s="12" t="n">
-        <v>6290.42</v>
+      <c r="E93" s="14" t="n">
+        <v>2146</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -27158,14 +28165,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D94" t="n">
         <v>1</v>
       </c>
-      <c r="E94" s="12" t="n">
-        <v>1619.96</v>
+      <c r="E94" s="14" t="n">
+        <v>6290.42</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -27181,14 +28191,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D95" t="n">
         <v>1</v>
       </c>
-      <c r="E95" s="12" t="n">
-        <v>861.66</v>
+      <c r="E95" s="14" t="n">
+        <v>1619.96</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -27199,19 +28212,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>Custodial</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>3</v>
-      </c>
-      <c r="E96" s="12" t="n">
-        <v>8838.17</v>
+        <v>1</v>
+      </c>
+      <c r="E96" s="14" t="n">
+        <v>861.66</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -27227,14 +28243,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Vehicle Accident</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
-      </c>
-      <c r="E97" s="12" t="n">
-        <v>5717.7</v>
+        <v>3</v>
+      </c>
+      <c r="E97" s="14" t="n">
+        <v>8838.17</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -27250,14 +28269,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Vehicle Accident</t>
         </is>
       </c>
       <c r="D98" t="n">
         <v>1</v>
       </c>
-      <c r="E98" s="12" t="n">
-        <v>5440.98</v>
+      <c r="E98" s="14" t="n">
+        <v>5717.7</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -27273,14 +28295,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Lifting</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D99" t="n">
         <v>1</v>
       </c>
-      <c r="E99" s="12" t="n">
-        <v>3392.44</v>
+      <c r="E99" s="14" t="n">
+        <v>5440.98</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -27296,14 +28321,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Burn</t>
+          <t>Lifting</t>
         </is>
       </c>
       <c r="D100" t="n">
         <v>1</v>
       </c>
-      <c r="E100" s="12" t="n">
-        <v>1452.05</v>
+      <c r="E100" s="14" t="n">
+        <v>3392.44</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -27314,19 +28342,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Food Service</t>
+          <t>Facilities</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Burn</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>3</v>
-      </c>
-      <c r="E101" s="12" t="n">
-        <v>10652.06</v>
+        <v>1</v>
+      </c>
+      <c r="E101" s="14" t="n">
+        <v>1452.05</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -27342,14 +28373,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
-      </c>
-      <c r="E102" s="12" t="n">
-        <v>560.5</v>
+        <v>3</v>
+      </c>
+      <c r="E102" s="14" t="n">
+        <v>10652.06</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -27360,19 +28394,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Grounds</t>
+          <t>Food Service</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D103" t="n">
         <v>1</v>
       </c>
-      <c r="E103" s="12" t="n">
-        <v>2551.58</v>
+      <c r="E103" s="14" t="n">
+        <v>560.5</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -27383,19 +28420,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Grounds</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
-      </c>
-      <c r="E104" s="12" t="n">
-        <v>4949.3</v>
+        <v>1</v>
+      </c>
+      <c r="E104" s="14" t="n">
+        <v>2551.58</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -27411,37 +28451,43 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Student Assault</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E105" s="14" t="n">
+        <v>4949.3</v>
+      </c>
+      <c r="F105" t="n">
         <v>1</v>
-      </c>
-      <c r="E105" s="12" t="n">
-        <v>3898.48</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Meadowbrook Middle School</t>
+          <t>Foothills High School</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Burn</t>
+          <t>Student Assault</t>
         </is>
       </c>
       <c r="D106" t="n">
         <v>1</v>
       </c>
-      <c r="E106" s="12" t="n">
-        <v>1602.72</v>
+      <c r="E106" s="14" t="n">
+        <v>3898.48</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -27452,19 +28498,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Burn</t>
         </is>
       </c>
       <c r="D107" t="n">
         <v>1</v>
       </c>
-      <c r="E107" s="12" t="n">
-        <v>13399.81</v>
+      <c r="E107" s="14" t="n">
+        <v>1602.72</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -27480,14 +28529,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Vehicle Accident</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D108" t="n">
         <v>1</v>
       </c>
-      <c r="E108" s="12" t="n">
-        <v>7612.91</v>
+      <c r="E108" s="14" t="n">
+        <v>13399.81</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -27503,14 +28555,17 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Repetitive Motion</t>
+          <t>Vehicle Accident</t>
         </is>
       </c>
       <c r="D109" t="n">
         <v>1</v>
       </c>
-      <c r="E109" s="12" t="n">
-        <v>5664.22</v>
+      <c r="E109" s="14" t="n">
+        <v>7612.91</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -27526,14 +28581,17 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Repetitive Motion</t>
         </is>
       </c>
       <c r="D110" t="n">
         <v>1</v>
       </c>
-      <c r="E110" s="12" t="n">
-        <v>3490.7</v>
+      <c r="E110" s="14" t="n">
+        <v>5664.22</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -27549,14 +28607,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Student Assault</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D111" t="n">
         <v>1</v>
       </c>
-      <c r="E111" s="12" t="n">
-        <v>2826</v>
+      <c r="E111" s="14" t="n">
+        <v>3490.7</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -27567,7 +28628,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Classroom/Instruction</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -27578,8 +28639,11 @@
       <c r="D112" t="n">
         <v>1</v>
       </c>
-      <c r="E112" s="12" t="n">
-        <v>3523.04</v>
+      <c r="E112" s="14" t="n">
+        <v>2826</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -27595,14 +28659,17 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Student Assault</t>
         </is>
       </c>
       <c r="D113" t="n">
         <v>1</v>
       </c>
-      <c r="E113" s="12" t="n">
-        <v>1252.16</v>
+      <c r="E113" s="14" t="n">
+        <v>3523.04</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -27618,14 +28685,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D114" t="n">
         <v>1</v>
       </c>
-      <c r="E114" s="12" t="n">
-        <v>1099</v>
+      <c r="E114" s="14" t="n">
+        <v>1252.16</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -27636,19 +28706,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Custodial</t>
+          <t>Classroom/Instruction</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Lifting</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>2</v>
-      </c>
-      <c r="E115" s="12" t="n">
-        <v>14318.46</v>
+        <v>1</v>
+      </c>
+      <c r="E115" s="14" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -27664,14 +28737,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Lifting</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1</v>
-      </c>
-      <c r="E116" s="12" t="n">
-        <v>3194.52</v>
+        <v>2</v>
+      </c>
+      <c r="E116" s="14" t="n">
+        <v>14318.46</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -27687,14 +28763,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D117" t="n">
         <v>1</v>
       </c>
-      <c r="E117" s="12" t="n">
-        <v>2103.17</v>
+      <c r="E117" s="14" t="n">
+        <v>3194.52</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -27710,14 +28789,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D118" t="n">
         <v>1</v>
       </c>
-      <c r="E118" s="12" t="n">
-        <v>1198.46</v>
+      <c r="E118" s="14" t="n">
+        <v>2103.17</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -27733,13 +28815,16 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Repetitive Motion</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D119" t="n">
         <v>1</v>
       </c>
-      <c r="E119" s="12" t="n">
+      <c r="E119" s="14" t="n">
+        <v>1198.46</v>
+      </c>
+      <c r="F119" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27751,19 +28836,24 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>Custodial</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Lifting</t>
+          <t>Repetitive Motion</t>
         </is>
       </c>
       <c r="D120" t="n">
         <v>1</v>
       </c>
-      <c r="E120" s="12" t="n">
-        <v>7779.24</v>
+      <c r="E120" s="17" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -27779,14 +28869,17 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Repetitive Motion</t>
+          <t>Lifting</t>
         </is>
       </c>
       <c r="D121" t="n">
         <v>1</v>
       </c>
-      <c r="E121" s="12" t="n">
-        <v>6159.25</v>
+      <c r="E121" s="14" t="n">
+        <v>7779.24</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -27802,14 +28895,17 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Vehicle Accident</t>
+          <t>Repetitive Motion</t>
         </is>
       </c>
       <c r="D122" t="n">
         <v>1</v>
       </c>
-      <c r="E122" s="12" t="n">
-        <v>4295.82</v>
+      <c r="E122" s="14" t="n">
+        <v>6159.25</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -27825,14 +28921,17 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Vehicle Accident</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>2</v>
-      </c>
-      <c r="E123" s="12" t="n">
-        <v>4031.96</v>
+        <v>1</v>
+      </c>
+      <c r="E123" s="14" t="n">
+        <v>4295.82</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -27848,14 +28947,17 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1</v>
-      </c>
-      <c r="E124" s="12" t="n">
-        <v>3077.03</v>
+        <v>2</v>
+      </c>
+      <c r="E124" s="14" t="n">
+        <v>4031.96</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -27866,19 +28968,22 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Food Service</t>
+          <t>Facilities</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D125" t="n">
         <v>1</v>
       </c>
-      <c r="E125" s="12" t="n">
-        <v>11766</v>
+      <c r="E125" s="14" t="n">
+        <v>3077.03</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -27894,14 +28999,17 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D126" t="n">
         <v>1</v>
       </c>
-      <c r="E126" s="12" t="n">
-        <v>10961</v>
+      <c r="E126" s="14" t="n">
+        <v>11766</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -27917,14 +29025,17 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D127" t="n">
         <v>1</v>
       </c>
-      <c r="E127" s="12" t="n">
-        <v>783.63</v>
+      <c r="E127" s="14" t="n">
+        <v>10961</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -27935,19 +29046,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Grounds</t>
+          <t>Food Service</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Lifting</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D128" t="n">
         <v>1</v>
       </c>
-      <c r="E128" s="12" t="n">
-        <v>4148</v>
+      <c r="E128" s="14" t="n">
+        <v>783.63</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -27963,14 +29077,17 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Lifting</t>
         </is>
       </c>
       <c r="D129" t="n">
         <v>1</v>
       </c>
-      <c r="E129" s="12" t="n">
-        <v>2157</v>
+      <c r="E129" s="14" t="n">
+        <v>4148</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -27986,14 +29103,17 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Student Assault</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D130" t="n">
         <v>1</v>
       </c>
-      <c r="E130" s="12" t="n">
-        <v>1473.18</v>
+      <c r="E130" s="14" t="n">
+        <v>2157</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -28009,14 +29129,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Student Assault</t>
         </is>
       </c>
       <c r="D131" t="n">
         <v>1</v>
       </c>
-      <c r="E131" s="12" t="n">
-        <v>906.21</v>
+      <c r="E131" s="14" t="n">
+        <v>1473.18</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -28027,19 +29150,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Grounds</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D132" t="n">
         <v>1</v>
       </c>
-      <c r="E132" s="12" t="n">
-        <v>4388</v>
+      <c r="E132" s="14" t="n">
+        <v>906.21</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -28055,25 +29181,28 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D133" t="n">
         <v>1</v>
       </c>
-      <c r="E133" s="12" t="n">
-        <v>1414.22</v>
+      <c r="E133" s="14" t="n">
+        <v>4388</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Prairie View High School</t>
+          <t>Meadowbrook Middle School</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -28082,10 +29211,13 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>2</v>
-      </c>
-      <c r="E134" s="12" t="n">
-        <v>3044.77</v>
+        <v>1</v>
+      </c>
+      <c r="E134" s="14" t="n">
+        <v>1414.22</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -28101,14 +29233,17 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
-      </c>
-      <c r="E135" s="12" t="n">
-        <v>2614.18</v>
+        <v>2</v>
+      </c>
+      <c r="E135" s="14" t="n">
+        <v>3044.77</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -28119,19 +29254,22 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Lifting</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D136" t="n">
         <v>1</v>
       </c>
-      <c r="E136" s="12" t="n">
-        <v>3183.23</v>
+      <c r="E136" s="14" t="n">
+        <v>2614.18</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -28142,19 +29280,22 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Classroom/Instruction</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Repetitive Motion</t>
+          <t>Lifting</t>
         </is>
       </c>
       <c r="D137" t="n">
         <v>1</v>
       </c>
-      <c r="E137" s="12" t="n">
-        <v>7398.11</v>
+      <c r="E137" s="14" t="n">
+        <v>3183.23</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -28170,14 +29311,17 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Student Assault</t>
+          <t>Repetitive Motion</t>
         </is>
       </c>
       <c r="D138" t="n">
         <v>1</v>
       </c>
-      <c r="E138" s="12" t="n">
-        <v>5896.87</v>
+      <c r="E138" s="14" t="n">
+        <v>7398.11</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -28193,14 +29337,17 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Lifting</t>
+          <t>Student Assault</t>
         </is>
       </c>
       <c r="D139" t="n">
         <v>1</v>
       </c>
-      <c r="E139" s="12" t="n">
-        <v>5326.33</v>
+      <c r="E139" s="14" t="n">
+        <v>5896.87</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -28216,14 +29363,17 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Lifting</t>
         </is>
       </c>
       <c r="D140" t="n">
         <v>1</v>
       </c>
-      <c r="E140" s="12" t="n">
-        <v>1343.8</v>
+      <c r="E140" s="14" t="n">
+        <v>5326.33</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -28234,7 +29384,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Custodial</t>
+          <t>Classroom/Instruction</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -28243,10 +29393,13 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>3</v>
-      </c>
-      <c r="E141" s="12" t="n">
-        <v>5063.1</v>
+        <v>1</v>
+      </c>
+      <c r="E141" s="14" t="n">
+        <v>1343.8</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -28257,19 +29410,22 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>Custodial</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Lifting</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>2</v>
-      </c>
-      <c r="E142" s="12" t="n">
-        <v>15625.9</v>
+        <v>3</v>
+      </c>
+      <c r="E142" s="14" t="n">
+        <v>5063.1</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -28285,14 +29441,17 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Burn</t>
+          <t>Lifting</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1</v>
-      </c>
-      <c r="E143" s="12" t="n">
-        <v>2612.25</v>
+        <v>2</v>
+      </c>
+      <c r="E143" s="14" t="n">
+        <v>15625.9</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -28308,14 +29467,17 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Burn</t>
         </is>
       </c>
       <c r="D144" t="n">
         <v>1</v>
       </c>
-      <c r="E144" s="12" t="n">
-        <v>2564.37</v>
+      <c r="E144" s="14" t="n">
+        <v>2612.25</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -28331,14 +29493,17 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D145" t="n">
         <v>1</v>
       </c>
-      <c r="E145" s="12" t="n">
-        <v>2100.72</v>
+      <c r="E145" s="14" t="n">
+        <v>2564.37</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -28349,19 +29514,22 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Food Service</t>
+          <t>Facilities</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Student Assault</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>2</v>
-      </c>
-      <c r="E146" s="12" t="n">
-        <v>7558.23</v>
+        <v>1</v>
+      </c>
+      <c r="E146" s="14" t="n">
+        <v>2100.72</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -28377,14 +29545,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Student Assault</t>
         </is>
       </c>
       <c r="D147" t="n">
         <v>2</v>
       </c>
-      <c r="E147" s="12" t="n">
-        <v>6540.799999999999</v>
+      <c r="E147" s="14" t="n">
+        <v>7558.23</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -28400,14 +29571,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D148" t="n">
         <v>2</v>
       </c>
-      <c r="E148" s="12" t="n">
-        <v>970.3800000000001</v>
+      <c r="E148" s="14" t="n">
+        <v>6540.799999999999</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -28418,19 +29592,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Grounds</t>
+          <t>Food Service</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D149" t="n">
         <v>2</v>
       </c>
-      <c r="E149" s="12" t="n">
-        <v>9560.290000000001</v>
+      <c r="E149" s="14" t="n">
+        <v>970.3800000000001</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -28446,14 +29623,17 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1</v>
-      </c>
-      <c r="E150" s="12" t="n">
-        <v>7771.58</v>
+        <v>2</v>
+      </c>
+      <c r="E150" s="14" t="n">
+        <v>9560.290000000001</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -28469,14 +29649,17 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D151" t="n">
         <v>1</v>
       </c>
-      <c r="E151" s="12" t="n">
-        <v>7551.8</v>
+      <c r="E151" s="14" t="n">
+        <v>7771.58</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -28492,14 +29675,17 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Student Assault</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D152" t="n">
         <v>1</v>
       </c>
-      <c r="E152" s="12" t="n">
-        <v>4359.32</v>
+      <c r="E152" s="14" t="n">
+        <v>7551.8</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -28515,14 +29701,17 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Student Assault</t>
         </is>
       </c>
       <c r="D153" t="n">
         <v>1</v>
       </c>
-      <c r="E153" s="12" t="n">
-        <v>1536.6</v>
+      <c r="E153" s="14" t="n">
+        <v>4359.32</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -28533,42 +29722,48 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Grounds</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Burn</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D154" t="n">
         <v>1</v>
       </c>
-      <c r="E154" s="12" t="n">
-        <v>638.59</v>
+      <c r="E154" s="14" t="n">
+        <v>1536.6</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Sunrise Elementary School</t>
+          <t>Prairie View High School</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Burn</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>5</v>
-      </c>
-      <c r="E155" s="12" t="n">
-        <v>21823.41</v>
+        <v>1</v>
+      </c>
+      <c r="E155" s="14" t="n">
+        <v>638.59</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -28584,14 +29779,17 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
-      </c>
-      <c r="E156" s="12" t="n">
-        <v>739.11</v>
+        <v>5</v>
+      </c>
+      <c r="E156" s="14" t="n">
+        <v>21823.41</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -28607,14 +29805,17 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D157" t="n">
         <v>1</v>
       </c>
-      <c r="E157" s="12" t="n">
-        <v>700.39</v>
+      <c r="E157" s="14" t="n">
+        <v>739.11</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -28625,19 +29826,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>2</v>
-      </c>
-      <c r="E158" s="12" t="n">
-        <v>4962.41</v>
+        <v>1</v>
+      </c>
+      <c r="E158" s="14" t="n">
+        <v>700.39</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -28653,14 +29857,17 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D159" t="n">
         <v>2</v>
       </c>
-      <c r="E159" s="12" t="n">
-        <v>2975.38</v>
+      <c r="E159" s="14" t="n">
+        <v>4962.41</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -28676,14 +29883,17 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1</v>
-      </c>
-      <c r="E160" s="12" t="n">
-        <v>2002.47</v>
+        <v>2</v>
+      </c>
+      <c r="E160" s="14" t="n">
+        <v>2975.38</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -28699,14 +29909,17 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D161" t="n">
         <v>1</v>
       </c>
-      <c r="E161" s="12" t="n">
-        <v>1611.56</v>
+      <c r="E161" s="14" t="n">
+        <v>2002.47</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -28717,19 +29930,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Classroom/Instruction</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>2</v>
-      </c>
-      <c r="E162" s="12" t="n">
-        <v>10328.46</v>
+        <v>1</v>
+      </c>
+      <c r="E162" s="14" t="n">
+        <v>1611.56</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -28745,14 +29961,17 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1</v>
-      </c>
-      <c r="E163" s="12" t="n">
-        <v>5338.1</v>
+        <v>2</v>
+      </c>
+      <c r="E163" s="14" t="n">
+        <v>10328.46</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -28768,14 +29987,17 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Vehicle Accident</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D164" t="n">
         <v>1</v>
       </c>
-      <c r="E164" s="12" t="n">
-        <v>4384.39</v>
+      <c r="E164" s="14" t="n">
+        <v>5338.1</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -28791,14 +30013,17 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Repetitive Motion</t>
+          <t>Vehicle Accident</t>
         </is>
       </c>
       <c r="D165" t="n">
         <v>1</v>
       </c>
-      <c r="E165" s="12" t="n">
-        <v>2955.19</v>
+      <c r="E165" s="14" t="n">
+        <v>4384.39</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -28814,14 +30039,17 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Lifting</t>
+          <t>Repetitive Motion</t>
         </is>
       </c>
       <c r="D166" t="n">
         <v>1</v>
       </c>
-      <c r="E166" s="12" t="n">
-        <v>2933.39</v>
+      <c r="E166" s="14" t="n">
+        <v>2955.19</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -28832,19 +30060,22 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Custodial</t>
+          <t>Classroom/Instruction</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Lifting</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>4</v>
-      </c>
-      <c r="E167" s="12" t="n">
-        <v>27845.83</v>
+        <v>1</v>
+      </c>
+      <c r="E167" s="14" t="n">
+        <v>2933.39</v>
+      </c>
+      <c r="F167" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -28860,14 +30091,17 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1</v>
-      </c>
-      <c r="E168" s="12" t="n">
-        <v>1707.65</v>
+        <v>4</v>
+      </c>
+      <c r="E168" s="14" t="n">
+        <v>27845.83</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -28883,14 +30117,17 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D169" t="n">
         <v>1</v>
       </c>
-      <c r="E169" s="12" t="n">
-        <v>1028.23</v>
+      <c r="E169" s="14" t="n">
+        <v>1707.65</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -28901,19 +30138,22 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>Custodial</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D170" t="n">
         <v>1</v>
       </c>
-      <c r="E170" s="12" t="n">
-        <v>7313.6</v>
+      <c r="E170" s="14" t="n">
+        <v>1028.23</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -28929,14 +30169,17 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Vehicle Accident</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D171" t="n">
         <v>1</v>
       </c>
-      <c r="E171" s="12" t="n">
-        <v>3836.36</v>
+      <c r="E171" s="14" t="n">
+        <v>7313.6</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -28952,14 +30195,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Vehicle Accident</t>
         </is>
       </c>
       <c r="D172" t="n">
         <v>1</v>
       </c>
-      <c r="E172" s="12" t="n">
-        <v>534.21</v>
+      <c r="E172" s="14" t="n">
+        <v>3836.36</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -28970,19 +30216,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Food Service</t>
+          <t>Facilities</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Repetitive Motion</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D173" t="n">
         <v>1</v>
       </c>
-      <c r="E173" s="12" t="n">
-        <v>5043.6</v>
+      <c r="E173" s="14" t="n">
+        <v>534.21</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -28998,14 +30247,17 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Repetitive Motion</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>2</v>
-      </c>
-      <c r="E174" s="12" t="n">
-        <v>4766.91</v>
+        <v>1</v>
+      </c>
+      <c r="E174" s="14" t="n">
+        <v>5043.6</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -29021,14 +30273,17 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1</v>
-      </c>
-      <c r="E175" s="12" t="n">
-        <v>3401.98</v>
+        <v>2</v>
+      </c>
+      <c r="E175" s="14" t="n">
+        <v>4766.91</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -29039,19 +30294,22 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Grounds</t>
+          <t>Food Service</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Lifting</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>2</v>
-      </c>
-      <c r="E176" s="12" t="n">
-        <v>6935.33</v>
+        <v>1</v>
+      </c>
+      <c r="E176" s="14" t="n">
+        <v>3401.98</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -29067,14 +30325,17 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Lifting</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1</v>
-      </c>
-      <c r="E177" s="12" t="n">
-        <v>5157.12</v>
+        <v>2</v>
+      </c>
+      <c r="E177" s="14" t="n">
+        <v>6935.33</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -29090,14 +30351,17 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D178" t="n">
         <v>1</v>
       </c>
-      <c r="E178" s="12" t="n">
-        <v>522.1900000000001</v>
+      <c r="E178" s="14" t="n">
+        <v>5157.12</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -29108,19 +30372,22 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Grounds</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>2</v>
-      </c>
-      <c r="E179" s="12" t="n">
-        <v>21163.88</v>
+        <v>1</v>
+      </c>
+      <c r="E179" s="14" t="n">
+        <v>522.1900000000001</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -29136,14 +30403,17 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1</v>
-      </c>
-      <c r="E180" s="12" t="n">
-        <v>1519.57</v>
+        <v>2</v>
+      </c>
+      <c r="E180" s="14" t="n">
+        <v>21163.88</v>
+      </c>
+      <c r="F180" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -29159,37 +30429,43 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D181" t="n">
         <v>1</v>
       </c>
-      <c r="E181" s="12" t="n">
-        <v>568.83</v>
+      <c r="E181" s="14" t="n">
+        <v>1519.57</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Timber Trail Elementary School</t>
+          <t>Sunrise Elementary School</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>3</v>
-      </c>
-      <c r="E182" s="12" t="n">
-        <v>30594.35</v>
+        <v>1</v>
+      </c>
+      <c r="E182" s="14" t="n">
+        <v>568.83</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -29205,14 +30481,17 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>2</v>
-      </c>
-      <c r="E183" s="12" t="n">
-        <v>8824.59</v>
+        <v>3</v>
+      </c>
+      <c r="E183" s="14" t="n">
+        <v>30594.35</v>
+      </c>
+      <c r="F183" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -29228,14 +30507,17 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Vehicle Accident</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1</v>
-      </c>
-      <c r="E184" s="12" t="n">
-        <v>6575.67</v>
+        <v>2</v>
+      </c>
+      <c r="E184" s="14" t="n">
+        <v>8824.59</v>
+      </c>
+      <c r="F184" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -29251,14 +30533,17 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Vehicle Accident</t>
         </is>
       </c>
       <c r="D185" t="n">
         <v>1</v>
       </c>
-      <c r="E185" s="12" t="n">
-        <v>5271</v>
+      <c r="E185" s="14" t="n">
+        <v>6575.67</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -29274,14 +30559,17 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Student Assault</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D186" t="n">
         <v>1</v>
       </c>
-      <c r="E186" s="12" t="n">
-        <v>3087.69</v>
+      <c r="E186" s="14" t="n">
+        <v>5271</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -29292,19 +30580,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Student Assault</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>3</v>
-      </c>
-      <c r="E187" s="12" t="n">
-        <v>23588.51</v>
+        <v>1</v>
+      </c>
+      <c r="E187" s="14" t="n">
+        <v>3087.69</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="188">
@@ -29320,14 +30611,17 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Vehicle Accident</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1</v>
-      </c>
-      <c r="E188" s="12" t="n">
-        <v>4690.83</v>
+        <v>3</v>
+      </c>
+      <c r="E188" s="14" t="n">
+        <v>23588.51</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -29343,14 +30637,17 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Student Assault</t>
+          <t>Vehicle Accident</t>
         </is>
       </c>
       <c r="D189" t="n">
         <v>1</v>
       </c>
-      <c r="E189" s="12" t="n">
-        <v>3245.43</v>
+      <c r="E189" s="14" t="n">
+        <v>4690.83</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -29366,14 +30663,17 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Student Assault</t>
         </is>
       </c>
       <c r="D190" t="n">
         <v>1</v>
       </c>
-      <c r="E190" s="12" t="n">
-        <v>3170</v>
+      <c r="E190" s="14" t="n">
+        <v>3245.43</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -29389,14 +30689,17 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D191" t="n">
         <v>1</v>
       </c>
-      <c r="E191" s="12" t="n">
-        <v>2191.28</v>
+      <c r="E191" s="14" t="n">
+        <v>3170</v>
+      </c>
+      <c r="F191" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -29412,14 +30715,17 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Burn</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D192" t="n">
         <v>1</v>
       </c>
-      <c r="E192" s="12" t="n">
-        <v>1087.01</v>
+      <c r="E192" s="14" t="n">
+        <v>2191.28</v>
+      </c>
+      <c r="F192" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -29435,14 +30741,17 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Burn</t>
         </is>
       </c>
       <c r="D193" t="n">
         <v>1</v>
       </c>
-      <c r="E193" s="12" t="n">
-        <v>981.89</v>
+      <c r="E193" s="14" t="n">
+        <v>1087.01</v>
+      </c>
+      <c r="F193" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -29453,19 +30762,22 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Classroom/Instruction</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>3</v>
-      </c>
-      <c r="E194" s="12" t="n">
-        <v>15221.6</v>
+        <v>1</v>
+      </c>
+      <c r="E194" s="14" t="n">
+        <v>981.89</v>
+      </c>
+      <c r="F194" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -29481,14 +30793,17 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Student Assault</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1</v>
-      </c>
-      <c r="E195" s="12" t="n">
-        <v>6983.55</v>
+        <v>3</v>
+      </c>
+      <c r="E195" s="14" t="n">
+        <v>15221.6</v>
+      </c>
+      <c r="F195" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -29504,14 +30819,17 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Student Assault</t>
         </is>
       </c>
       <c r="D196" t="n">
         <v>1</v>
       </c>
-      <c r="E196" s="12" t="n">
-        <v>4944.27</v>
+      <c r="E196" s="14" t="n">
+        <v>6983.55</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -29527,14 +30845,17 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Lifting</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D197" t="n">
         <v>1</v>
       </c>
-      <c r="E197" s="12" t="n">
-        <v>3205.26</v>
+      <c r="E197" s="14" t="n">
+        <v>4944.27</v>
+      </c>
+      <c r="F197" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -29545,7 +30866,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Custodial</t>
+          <t>Classroom/Instruction</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -29554,10 +30875,13 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>3</v>
-      </c>
-      <c r="E198" s="12" t="n">
-        <v>28548.57</v>
+        <v>1</v>
+      </c>
+      <c r="E198" s="14" t="n">
+        <v>3205.26</v>
+      </c>
+      <c r="F198" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -29573,14 +30897,17 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Lifting</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>4</v>
-      </c>
-      <c r="E199" s="12" t="n">
-        <v>11785.91</v>
+        <v>3</v>
+      </c>
+      <c r="E199" s="14" t="n">
+        <v>28548.57</v>
+      </c>
+      <c r="F199" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -29596,14 +30923,17 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1</v>
-      </c>
-      <c r="E200" s="12" t="n">
-        <v>2463</v>
+        <v>4</v>
+      </c>
+      <c r="E200" s="14" t="n">
+        <v>11785.91</v>
+      </c>
+      <c r="F200" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -29619,14 +30949,17 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Repetitive Motion</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D201" t="n">
         <v>1</v>
       </c>
-      <c r="E201" s="12" t="n">
-        <v>2361.25</v>
+      <c r="E201" s="14" t="n">
+        <v>2463</v>
+      </c>
+      <c r="F201" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -29637,19 +30970,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>Custodial</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Repetitive Motion</t>
         </is>
       </c>
       <c r="D202" t="n">
         <v>1</v>
       </c>
-      <c r="E202" s="12" t="n">
-        <v>3879.31</v>
+      <c r="E202" s="14" t="n">
+        <v>2361.25</v>
+      </c>
+      <c r="F202" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -29665,14 +31001,17 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D203" t="n">
         <v>1</v>
       </c>
-      <c r="E203" s="12" t="n">
-        <v>1821.64</v>
+      <c r="E203" s="14" t="n">
+        <v>3879.31</v>
+      </c>
+      <c r="F203" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -29688,14 +31027,17 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D204" t="n">
         <v>1</v>
       </c>
-      <c r="E204" s="12" t="n">
-        <v>527</v>
+      <c r="E204" s="14" t="n">
+        <v>1821.64</v>
+      </c>
+      <c r="F204" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -29706,19 +31048,22 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Food Service</t>
+          <t>Facilities</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>4</v>
-      </c>
-      <c r="E205" s="12" t="n">
-        <v>18103.69</v>
+        <v>1</v>
+      </c>
+      <c r="E205" s="14" t="n">
+        <v>527</v>
+      </c>
+      <c r="F205" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -29729,7 +31074,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Grounds</t>
+          <t>Food Service</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -29738,10 +31083,13 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>3</v>
-      </c>
-      <c r="E206" s="12" t="n">
-        <v>17336.1</v>
+        <v>4</v>
+      </c>
+      <c r="E206" s="14" t="n">
+        <v>18103.69</v>
+      </c>
+      <c r="F206" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -29757,14 +31105,17 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Lifting</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1</v>
-      </c>
-      <c r="E207" s="12" t="n">
-        <v>4511.14</v>
+        <v>3</v>
+      </c>
+      <c r="E207" s="14" t="n">
+        <v>17336.1</v>
+      </c>
+      <c r="F207" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -29780,14 +31131,17 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Lifting</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>2</v>
-      </c>
-      <c r="E208" s="12" t="n">
-        <v>3228.31</v>
+        <v>1</v>
+      </c>
+      <c r="E208" s="14" t="n">
+        <v>4511.14</v>
+      </c>
+      <c r="F208" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="209">
@@ -29803,14 +31157,17 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1</v>
-      </c>
-      <c r="E209" s="12" t="n">
-        <v>2388.59</v>
+        <v>2</v>
+      </c>
+      <c r="E209" s="14" t="n">
+        <v>3228.31</v>
+      </c>
+      <c r="F209" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="210">
@@ -29821,19 +31178,22 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Grounds</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>2</v>
-      </c>
-      <c r="E210" s="12" t="n">
-        <v>12976.81</v>
+        <v>1</v>
+      </c>
+      <c r="E210" s="14" t="n">
+        <v>2388.59</v>
+      </c>
+      <c r="F210" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -29849,14 +31209,17 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Vehicle Accident</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1</v>
-      </c>
-      <c r="E211" s="12" t="n">
-        <v>4881.53</v>
+        <v>2</v>
+      </c>
+      <c r="E211" s="14" t="n">
+        <v>12976.81</v>
+      </c>
+      <c r="F211" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="212">
@@ -29872,37 +31235,43 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Vehicle Accident</t>
         </is>
       </c>
       <c r="D212" t="n">
         <v>1</v>
       </c>
-      <c r="E212" s="12" t="n">
-        <v>3206.71</v>
+      <c r="E212" s="14" t="n">
+        <v>4881.53</v>
+      </c>
+      <c r="F212" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Vivekananda International Academy</t>
+          <t>Timber Trail Elementary School</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Repetitive Motion</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>2</v>
-      </c>
-      <c r="E213" s="12" t="n">
-        <v>6090.83</v>
+        <v>1</v>
+      </c>
+      <c r="E213" s="14" t="n">
+        <v>3206.71</v>
+      </c>
+      <c r="F213" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -29918,14 +31287,17 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Repetitive Motion</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1</v>
-      </c>
-      <c r="E214" s="12" t="n">
-        <v>3026.1</v>
+        <v>2</v>
+      </c>
+      <c r="E214" s="14" t="n">
+        <v>6090.83</v>
+      </c>
+      <c r="F214" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -29936,7 +31308,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -29947,8 +31319,11 @@
       <c r="D215" t="n">
         <v>1</v>
       </c>
-      <c r="E215" s="12" t="n">
-        <v>2067.56</v>
+      <c r="E215" s="14" t="n">
+        <v>3026.1</v>
+      </c>
+      <c r="F215" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -29964,14 +31339,17 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D216" t="n">
         <v>1</v>
       </c>
-      <c r="E216" s="12" t="n">
-        <v>1868.96</v>
+      <c r="E216" s="14" t="n">
+        <v>2067.56</v>
+      </c>
+      <c r="F216" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -29987,14 +31365,17 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D217" t="n">
         <v>1</v>
       </c>
-      <c r="E217" s="12" t="n">
-        <v>1265.14</v>
+      <c r="E217" s="14" t="n">
+        <v>1868.96</v>
+      </c>
+      <c r="F217" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -30005,19 +31386,22 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Classroom/Instruction</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D218" t="n">
         <v>1</v>
       </c>
-      <c r="E218" s="12" t="n">
-        <v>9585</v>
+      <c r="E218" s="14" t="n">
+        <v>1265.14</v>
+      </c>
+      <c r="F218" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -30033,14 +31417,17 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Repetitive Motion</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>2</v>
-      </c>
-      <c r="E219" s="12" t="n">
-        <v>6371.709999999999</v>
+        <v>1</v>
+      </c>
+      <c r="E219" s="14" t="n">
+        <v>9585</v>
+      </c>
+      <c r="F219" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="220">
@@ -30056,14 +31443,17 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Repetitive Motion</t>
         </is>
       </c>
       <c r="D220" t="n">
         <v>2</v>
       </c>
-      <c r="E220" s="12" t="n">
-        <v>3800.13</v>
+      <c r="E220" s="14" t="n">
+        <v>6371.709999999999</v>
+      </c>
+      <c r="F220" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -30074,19 +31464,22 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Custodial</t>
+          <t>Classroom/Instruction</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D221" t="n">
         <v>2</v>
       </c>
-      <c r="E221" s="12" t="n">
-        <v>10804.56</v>
+      <c r="E221" s="14" t="n">
+        <v>3800.13</v>
+      </c>
+      <c r="F221" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -30102,14 +31495,17 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Repetitive Motion</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1</v>
-      </c>
-      <c r="E222" s="12" t="n">
-        <v>4599.35</v>
+        <v>2</v>
+      </c>
+      <c r="E222" s="14" t="n">
+        <v>10804.56</v>
+      </c>
+      <c r="F222" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="223">
@@ -30125,14 +31521,17 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Lifting</t>
+          <t>Repetitive Motion</t>
         </is>
       </c>
       <c r="D223" t="n">
         <v>1</v>
       </c>
-      <c r="E223" s="12" t="n">
-        <v>4430.5</v>
+      <c r="E223" s="14" t="n">
+        <v>4599.35</v>
+      </c>
+      <c r="F223" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -30143,7 +31542,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>Custodial</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -30152,10 +31551,13 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>3</v>
-      </c>
-      <c r="E224" s="12" t="n">
-        <v>17312.62</v>
+        <v>1</v>
+      </c>
+      <c r="E224" s="14" t="n">
+        <v>4430.5</v>
+      </c>
+      <c r="F224" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="225">
@@ -30171,14 +31573,17 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Lifting</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1</v>
-      </c>
-      <c r="E225" s="12" t="n">
-        <v>3492.26</v>
+        <v>3</v>
+      </c>
+      <c r="E225" s="14" t="n">
+        <v>17312.62</v>
+      </c>
+      <c r="F225" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="226">
@@ -30194,14 +31599,17 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D226" t="n">
         <v>1</v>
       </c>
-      <c r="E226" s="12" t="n">
-        <v>1516.29</v>
+      <c r="E226" s="14" t="n">
+        <v>3492.26</v>
+      </c>
+      <c r="F226" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="227">
@@ -30212,19 +31620,22 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Food Service</t>
+          <t>Facilities</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D227" t="n">
         <v>1</v>
       </c>
-      <c r="E227" s="12" t="n">
-        <v>3365.29</v>
+      <c r="E227" s="14" t="n">
+        <v>1516.29</v>
+      </c>
+      <c r="F227" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="228">
@@ -30240,14 +31651,17 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Burn</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D228" t="n">
         <v>1</v>
       </c>
-      <c r="E228" s="12" t="n">
-        <v>3201.73</v>
+      <c r="E228" s="14" t="n">
+        <v>3365.29</v>
+      </c>
+      <c r="F228" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="229">
@@ -30263,14 +31677,17 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Burn</t>
         </is>
       </c>
       <c r="D229" t="n">
         <v>1</v>
       </c>
-      <c r="E229" s="12" t="n">
-        <v>2687.46</v>
+      <c r="E229" s="14" t="n">
+        <v>3201.73</v>
+      </c>
+      <c r="F229" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -30286,14 +31703,17 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Lifting</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D230" t="n">
         <v>1</v>
       </c>
-      <c r="E230" s="12" t="n">
-        <v>2421.45</v>
+      <c r="E230" s="14" t="n">
+        <v>2687.46</v>
+      </c>
+      <c r="F230" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="231">
@@ -30309,13 +31729,16 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Repetitive Motion</t>
+          <t>Lifting</t>
         </is>
       </c>
       <c r="D231" t="n">
         <v>1</v>
       </c>
-      <c r="E231" s="12" t="n">
+      <c r="E231" s="14" t="n">
+        <v>2421.45</v>
+      </c>
+      <c r="F231" t="n">
         <v>0</v>
       </c>
     </row>
@@ -30327,19 +31750,24 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Grounds</t>
+          <t>Food Service</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Lifting</t>
+          <t>Repetitive Motion</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>2</v>
-      </c>
-      <c r="E232" s="12" t="n">
-        <v>16057.91</v>
+        <v>1</v>
+      </c>
+      <c r="E232" s="17" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="233">
@@ -30355,14 +31783,17 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Vehicle Accident</t>
+          <t>Lifting</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1</v>
-      </c>
-      <c r="E233" s="12" t="n">
-        <v>10089.9</v>
+        <v>2</v>
+      </c>
+      <c r="E233" s="14" t="n">
+        <v>16057.91</v>
+      </c>
+      <c r="F233" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -30378,14 +31809,17 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Student Assault</t>
+          <t>Vehicle Accident</t>
         </is>
       </c>
       <c r="D234" t="n">
         <v>1</v>
       </c>
-      <c r="E234" s="12" t="n">
-        <v>3256.59</v>
+      <c r="E234" s="14" t="n">
+        <v>10089.9</v>
+      </c>
+      <c r="F234" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="235">
@@ -30396,19 +31830,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Grounds</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Student Assault</t>
         </is>
       </c>
       <c r="D235" t="n">
         <v>1</v>
       </c>
-      <c r="E235" s="12" t="n">
-        <v>5797.32</v>
+      <c r="E235" s="14" t="n">
+        <v>3256.59</v>
+      </c>
+      <c r="F235" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="236">
@@ -30424,14 +31861,17 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D236" t="n">
         <v>1</v>
       </c>
-      <c r="E236" s="12" t="n">
-        <v>4749.49</v>
+      <c r="E236" s="14" t="n">
+        <v>5797.32</v>
+      </c>
+      <c r="F236" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -30447,37 +31887,43 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Burn</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D237" t="n">
         <v>1</v>
       </c>
-      <c r="E237" s="12" t="n">
-        <v>2542.12</v>
+      <c r="E237" s="14" t="n">
+        <v>4749.49</v>
+      </c>
+      <c r="F237" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Willow Creek Elementary School</t>
+          <t>Vivekananda International Academy</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Lifting</t>
+          <t>Burn</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>2</v>
-      </c>
-      <c r="E238" s="12" t="n">
-        <v>12935.96</v>
+        <v>1</v>
+      </c>
+      <c r="E238" s="14" t="n">
+        <v>2542.12</v>
+      </c>
+      <c r="F238" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -30493,14 +31939,17 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Lifting</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>3</v>
-      </c>
-      <c r="E239" s="12" t="n">
-        <v>10740.68</v>
+        <v>2</v>
+      </c>
+      <c r="E239" s="14" t="n">
+        <v>12935.96</v>
+      </c>
+      <c r="F239" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -30516,14 +31965,17 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Student Assault</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D240" t="n">
+        <v>3</v>
+      </c>
+      <c r="E240" s="14" t="n">
+        <v>10740.68</v>
+      </c>
+      <c r="F240" t="n">
         <v>1</v>
-      </c>
-      <c r="E240" s="12" t="n">
-        <v>7997.23</v>
       </c>
     </row>
     <row r="241">
@@ -30539,14 +31991,17 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Repetitive Motion</t>
+          <t>Student Assault</t>
         </is>
       </c>
       <c r="D241" t="n">
         <v>1</v>
       </c>
-      <c r="E241" s="12" t="n">
-        <v>1966.91</v>
+      <c r="E241" s="14" t="n">
+        <v>7997.23</v>
+      </c>
+      <c r="F241" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -30562,14 +32017,17 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Repetitive Motion</t>
         </is>
       </c>
       <c r="D242" t="n">
         <v>1</v>
       </c>
-      <c r="E242" s="12" t="n">
-        <v>1026.2</v>
+      <c r="E242" s="14" t="n">
+        <v>1966.91</v>
+      </c>
+      <c r="F242" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -30580,19 +32038,22 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Lifting</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D243" t="n">
         <v>1</v>
       </c>
-      <c r="E243" s="12" t="n">
-        <v>14097.98</v>
+      <c r="E243" s="14" t="n">
+        <v>1026.2</v>
+      </c>
+      <c r="F243" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -30608,14 +32069,17 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Lifting</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>2</v>
-      </c>
-      <c r="E244" s="12" t="n">
-        <v>7551.95</v>
+        <v>1</v>
+      </c>
+      <c r="E244" s="14" t="n">
+        <v>14097.98</v>
+      </c>
+      <c r="F244" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="245">
@@ -30631,14 +32095,17 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>3</v>
-      </c>
-      <c r="E245" s="12" t="n">
-        <v>7535.549999999999</v>
+        <v>2</v>
+      </c>
+      <c r="E245" s="14" t="n">
+        <v>7551.95</v>
+      </c>
+      <c r="F245" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -30654,14 +32121,17 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>1</v>
-      </c>
-      <c r="E246" s="12" t="n">
-        <v>3748.23</v>
+        <v>3</v>
+      </c>
+      <c r="E246" s="14" t="n">
+        <v>7535.549999999999</v>
+      </c>
+      <c r="F246" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -30672,19 +32142,22 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Classroom/Instruction</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>3</v>
-      </c>
-      <c r="E247" s="12" t="n">
-        <v>21083.11</v>
+        <v>1</v>
+      </c>
+      <c r="E247" s="14" t="n">
+        <v>3748.23</v>
+      </c>
+      <c r="F247" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -30700,14 +32173,17 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>1</v>
-      </c>
-      <c r="E248" s="12" t="n">
-        <v>766.36</v>
+        <v>3</v>
+      </c>
+      <c r="E248" s="14" t="n">
+        <v>21083.11</v>
+      </c>
+      <c r="F248" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -30718,19 +32194,22 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Custodial</t>
+          <t>Classroom/Instruction</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Student Assault</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D249" t="n">
         <v>1</v>
       </c>
-      <c r="E249" s="12" t="n">
-        <v>8961.26</v>
+      <c r="E249" s="14" t="n">
+        <v>766.36</v>
+      </c>
+      <c r="F249" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -30746,14 +32225,17 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Student Assault</t>
         </is>
       </c>
       <c r="D250" t="n">
         <v>1</v>
       </c>
-      <c r="E250" s="12" t="n">
-        <v>3726.77</v>
+      <c r="E250" s="14" t="n">
+        <v>8961.26</v>
+      </c>
+      <c r="F250" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="251">
@@ -30769,14 +32251,17 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Vehicle Accident</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D251" t="n">
         <v>1</v>
       </c>
-      <c r="E251" s="12" t="n">
-        <v>3605.19</v>
+      <c r="E251" s="14" t="n">
+        <v>3726.77</v>
+      </c>
+      <c r="F251" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -30792,14 +32277,17 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Lifting</t>
+          <t>Vehicle Accident</t>
         </is>
       </c>
       <c r="D252" t="n">
         <v>1</v>
       </c>
-      <c r="E252" s="12" t="n">
-        <v>3590.66</v>
+      <c r="E252" s="14" t="n">
+        <v>3605.19</v>
+      </c>
+      <c r="F252" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -30815,14 +32303,17 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Lifting</t>
         </is>
       </c>
       <c r="D253" t="n">
         <v>1</v>
       </c>
-      <c r="E253" s="12" t="n">
-        <v>1125.98</v>
+      <c r="E253" s="14" t="n">
+        <v>3590.66</v>
+      </c>
+      <c r="F253" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="254">
@@ -30838,14 +32329,17 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D254" t="n">
         <v>1</v>
       </c>
-      <c r="E254" s="12" t="n">
-        <v>881.5700000000001</v>
+      <c r="E254" s="14" t="n">
+        <v>1125.98</v>
+      </c>
+      <c r="F254" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="255">
@@ -30861,13 +32355,16 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D255" t="n">
         <v>1</v>
       </c>
-      <c r="E255" s="12" t="n">
+      <c r="E255" s="14" t="n">
+        <v>881.5700000000001</v>
+      </c>
+      <c r="F255" t="n">
         <v>0</v>
       </c>
     </row>
@@ -30879,19 +32376,24 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>Custodial</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>3</v>
-      </c>
-      <c r="E256" s="12" t="n">
-        <v>14517.96</v>
+        <v>1</v>
+      </c>
+      <c r="E256" s="17" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F256" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="257">
@@ -30907,14 +32409,17 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Burn</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>1</v>
-      </c>
-      <c r="E257" s="12" t="n">
-        <v>1892.02</v>
+        <v>3</v>
+      </c>
+      <c r="E257" s="14" t="n">
+        <v>14517.96</v>
+      </c>
+      <c r="F257" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="258">
@@ -30925,19 +32430,22 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Food Service</t>
+          <t>Facilities</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Burn</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>2</v>
-      </c>
-      <c r="E258" s="12" t="n">
-        <v>14952.5</v>
+        <v>1</v>
+      </c>
+      <c r="E258" s="14" t="n">
+        <v>1892.02</v>
+      </c>
+      <c r="F258" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="259">
@@ -30953,14 +32461,17 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Student Assault</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>1</v>
-      </c>
-      <c r="E259" s="12" t="n">
-        <v>5335.92</v>
+        <v>2</v>
+      </c>
+      <c r="E259" s="14" t="n">
+        <v>14952.5</v>
+      </c>
+      <c r="F259" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -30976,14 +32487,17 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Burn</t>
+          <t>Student Assault</t>
         </is>
       </c>
       <c r="D260" t="n">
         <v>1</v>
       </c>
-      <c r="E260" s="12" t="n">
-        <v>4352.77</v>
+      <c r="E260" s="14" t="n">
+        <v>5335.92</v>
+      </c>
+      <c r="F260" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="261">
@@ -30999,14 +32513,17 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Burn</t>
         </is>
       </c>
       <c r="D261" t="n">
         <v>1</v>
       </c>
-      <c r="E261" s="12" t="n">
-        <v>2034.61</v>
+      <c r="E261" s="14" t="n">
+        <v>4352.77</v>
+      </c>
+      <c r="F261" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -31017,19 +32534,22 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Grounds</t>
+          <t>Food Service</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>3</v>
-      </c>
-      <c r="E262" s="12" t="n">
-        <v>17827.82</v>
+        <v>1</v>
+      </c>
+      <c r="E262" s="14" t="n">
+        <v>2034.61</v>
+      </c>
+      <c r="F262" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -31045,14 +32565,17 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Struck By/Against</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>1</v>
-      </c>
-      <c r="E263" s="12" t="n">
-        <v>1160.33</v>
+        <v>3</v>
+      </c>
+      <c r="E263" s="14" t="n">
+        <v>17827.82</v>
+      </c>
+      <c r="F263" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="264">
@@ -31063,19 +32586,22 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Grounds</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Student Assault</t>
+          <t>Struck By/Against</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>2</v>
-      </c>
-      <c r="E264" s="12" t="n">
-        <v>12116.07</v>
+        <v>1</v>
+      </c>
+      <c r="E264" s="14" t="n">
+        <v>1160.33</v>
+      </c>
+      <c r="F264" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -31091,14 +32617,17 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Slip/Fall</t>
+          <t>Student Assault</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>1</v>
-      </c>
-      <c r="E265" s="12" t="n">
-        <v>3923.92</v>
+        <v>2</v>
+      </c>
+      <c r="E265" s="14" t="n">
+        <v>12116.07</v>
+      </c>
+      <c r="F265" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="266">
@@ -31114,14 +32643,17 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Cut/Laceration</t>
+          <t>Slip/Fall</t>
         </is>
       </c>
       <c r="D266" t="n">
         <v>1</v>
       </c>
-      <c r="E266" s="12" t="n">
-        <v>3298.42</v>
+      <c r="E266" s="14" t="n">
+        <v>3923.92</v>
+      </c>
+      <c r="F266" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="267">
@@ -31137,18 +32669,47 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Cut/Laceration</t>
         </is>
       </c>
       <c r="D267" t="n">
         <v>1</v>
       </c>
-      <c r="E267" s="12" t="n">
+      <c r="E267" s="14" t="n">
+        <v>3298.42</v>
+      </c>
+      <c r="F267" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Willow Creek Elementary School</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>1</v>
+      </c>
+      <c r="E268" s="14" t="n">
         <v>2439.68</v>
       </c>
+      <c r="F268" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E4:E267">
+  <conditionalFormatting sqref="E5:E268">
     <cfRule type="top10" rank="10" priority="1" dxfId="0" percent="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/claims_dashboard.xlsx
+++ b/claims_dashboard.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/NikiChoksi/Documents/Niki/Projects/ClaimsAnalytics/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/NikiChoksi/Documents/Niki/Projects/ClaimsAnalytics/Claims_Analytics_Portfolio_NikiChoksi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63D060D-FEC9-DF48-867F-D5F3352E8C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D84DAA1D-3942-F543-8820-E83C8EE68D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17540" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17540" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
   </definedNames>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId6"/>
+    <pivotCache cacheId="2" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4632" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4640" uniqueCount="502">
   <si>
     <t>ClaimId</t>
   </si>
@@ -1498,7 +1498,7 @@
     <t>DATA QUALITY: 400 raw records -&gt; 15 exact duplicates removed -&gt; 3 missing IDs retained as UNASSIGNED-### -&gt; 10 exceptions quarantined -&gt; 375 clean records, of which 6 are pending a loss estimate (blank reserve, not zero). Full audit trail: claims_cleaning_log.xlsx.</t>
   </si>
   <si>
-    <t>NOTE: Slicers (School Level / Department / Status) require a live PivotTable connected to the "Data" sheet's ClaimsData table - see dashboard_pivot_slicer_guide.txt for exact steps.</t>
+    <t>KPI cards above reflect the full district (all 375 claims) as of the reporting period. The slicers below (School Level / Department / Status) filter the interactive Pivot_Base drill-down view, not the KPI cards - see dashboard_pivot_slicer_guide.txt for how they were built via build_live_dashboard.bas.</t>
   </si>
   <si>
     <t>Claims Trends</t>
@@ -1557,10 +1557,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="[$-409]\$#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="[$-409]\$#,##0"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="[$-409]\$#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="[$-409]\$#,##0"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -1575,58 +1575,68 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FF1F4E78"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF595959"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="22"/>
       <color rgb="FF1F4E78"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="22"/>
       <color rgb="FF9C5700"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF375623"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9.5"/>
       <color rgb="FF1F4E78"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9.5"/>
       <color rgb="FF808080"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1676,13 +1686,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1691,10 +1701,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1702,11 +1716,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3300,7 +3309,7 @@
             <c:numRef>
               <c:f>Trends!$B$43:$B$53</c:f>
               <c:numCache>
-                <c:formatCode>\$#,##0</c:formatCode>
+                <c:formatCode>[$-409]\$#,##0</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>275674.01</c:v>
@@ -3778,7 +3787,7 @@
             <c:numRef>
               <c:f>Trends!$B$99:$B$108</c:f>
               <c:numCache>
-                <c:formatCode>\$#,##0</c:formatCode>
+                <c:formatCode>[$-409]\$#,##0</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>249306.76</c:v>
@@ -4432,19 +4441,19 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>84781</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>982869</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>173129</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>840946</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>88214</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>752597</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>10910</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="4" name="SchoolLevel">
@@ -4467,7 +4476,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -4477,8 +4486,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="8698694"/>
-              <a:ext cx="1912163" cy="1505346"/>
+              <a:off x="4637647" y="638796"/>
+              <a:ext cx="1914617" cy="1559336"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -4510,19 +4519,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>235106</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>38176</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>201976</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>159653</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>4126</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>41609</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1042214</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>361869</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="5" name="Department">
@@ -4545,7 +4554,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -4555,8 +4564,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2377541" y="8652089"/>
-              <a:ext cx="1911455" cy="1505346"/>
+              <a:off x="7074087" y="625320"/>
+              <a:ext cx="1912683" cy="1556882"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -4588,19 +4597,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>318743</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>166341</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>385003</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>688</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>87762</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>169774</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>154021</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>26208</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="6" name="ClaimStatus">
@@ -4623,7 +4632,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -4633,8 +4642,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4603613" y="8592515"/>
-              <a:ext cx="1911453" cy="1505346"/>
+              <a:off x="9402003" y="663910"/>
+              <a:ext cx="1913907" cy="1549520"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -4805,7 +4814,7 @@
     <cacheField name="ClaimId" numFmtId="0">
       <sharedItems/>
     </cacheField>
-    <cacheField name="ReportDate" numFmtId="165">
+    <cacheField name="ReportDate" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2024-08-02T00:00:00" maxDate="2025-07-31T00:00:00"/>
     </cacheField>
     <cacheField name="SchoolSite" numFmtId="0">
@@ -4843,7 +4852,7 @@
         <s v="Re-opened"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="IncurredLoss" numFmtId="166">
+    <cacheField name="IncurredLoss" numFmtId="165">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="403.93" maxValue="21462"/>
     </cacheField>
     <cacheField name="LossIsEstimatePending" numFmtId="0">
@@ -10498,30 +10507,30 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{34E78ABF-4FC7-6E43-BF06-B3B80CA3B572}" name="PT_Master" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:E7" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{34E78ABF-4FC7-6E43-BF06-B3B80CA3B572}" name="PT_Master" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:I9" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
       <items count="4">
         <item x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
+        <item x="0"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0">
       <items count="9">
         <item x="7"/>
-        <item h="1" x="5"/>
-        <item h="1" x="6"/>
-        <item h="1" x="3"/>
-        <item h="1" x="4"/>
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item h="1" x="0"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -10529,9 +10538,9 @@
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="4">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="1"/>
-        <item h="1" x="2"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -10544,9 +10553,15 @@
   <rowFields count="1">
     <field x="7"/>
   </rowFields>
-  <rowItems count="2">
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
     <i>
       <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
     </i>
     <i t="grand">
       <x/>
@@ -10556,9 +10571,23 @@
     <field x="3"/>
     <field x="-2"/>
   </colFields>
-  <colItems count="4">
+  <colItems count="8">
     <i>
       <x/>
+      <x/>
+    </i>
+    <i r="1" i="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="1"/>
+      <x/>
+    </i>
+    <i r="1" i="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
       <x/>
     </i>
     <i r="1" i="1">
@@ -10596,8 +10625,8 @@
     <tabular pivotCacheId="1084199705">
       <items count="3">
         <i x="1" s="1"/>
-        <i x="0"/>
-        <i x="2"/>
+        <i x="0" s="1"/>
+        <i x="2" s="1"/>
       </items>
     </tabular>
   </data>
@@ -10613,13 +10642,13 @@
     <tabular pivotCacheId="1084199705">
       <items count="8">
         <i x="7" s="1"/>
-        <i x="5"/>
-        <i x="6"/>
-        <i x="3"/>
-        <i x="4"/>
-        <i x="2"/>
-        <i x="1"/>
-        <i x="0"/>
+        <i x="5" s="1"/>
+        <i x="6" s="1"/>
+        <i x="3" s="1"/>
+        <i x="4" s="1"/>
+        <i x="2" s="1"/>
+        <i x="1" s="1"/>
+        <i x="0" s="1"/>
       </items>
     </tabular>
   </data>
@@ -10634,9 +10663,9 @@
   <data>
     <tabular pivotCacheId="1084199705">
       <items count="3">
-        <i x="0"/>
+        <i x="0" s="1"/>
         <i x="1" s="1"/>
-        <i x="2"/>
+        <i x="2" s="1"/>
       </items>
     </tabular>
   </data>
@@ -26324,7 +26353,10 @@
   <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="13" width="14" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="13" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -26341,56 +26373,52 @@
       <c r="A4" s="6" t="s">
         <v>460</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="D4" s="6" t="s">
+      <c r="B4" s="6" t="s">
         <v>461</v>
       </c>
+      <c r="C4" s="6" t="s">
+        <v>462</v>
+      </c>
       <c r="E4" s="7"/>
-      <c r="G4" s="6" t="s">
-        <v>462</v>
-      </c>
       <c r="H4" s="7"/>
     </row>
     <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>463</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="D5" s="8" t="s">
+      <c r="B5" s="8" t="s">
         <v>464</v>
       </c>
+      <c r="C5" s="8" t="s">
+        <v>465</v>
+      </c>
       <c r="E5" s="7"/>
-      <c r="G5" s="8" t="s">
-        <v>465</v>
-      </c>
       <c r="H5" s="7"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="D8" s="6" t="s">
+      <c r="B8" s="6" t="s">
         <v>467</v>
       </c>
+      <c r="C8" s="6" t="s">
+        <v>468</v>
+      </c>
       <c r="E8" s="7"/>
-      <c r="G8" s="6" t="s">
-        <v>468</v>
-      </c>
       <c r="H8" s="7"/>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
         <v>469</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="D9" s="8" t="s">
+      <c r="B9" s="8" t="s">
         <v>470</v>
       </c>
+      <c r="C9" s="8" t="s">
+        <v>471</v>
+      </c>
       <c r="E9" s="7"/>
-      <c r="G9" s="8" t="s">
-        <v>471</v>
-      </c>
       <c r="H9" s="7"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -26413,7 +26441,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="96" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="80" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>476</v>
       </c>
@@ -26476,38 +26504,38 @@
       </c>
     </row>
     <row r="33" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="18" t="s">
         <v>483</v>
       </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
-      <c r="M33" s="17"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
+      <c r="M33" s="19"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="20" t="s">
         <v>484</v>
       </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+      <c r="M35" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -32492,38 +32520,44 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F2C47C2-71B1-7341-9B73-259726F816DE}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A3:E7"/>
+  <dimension ref="A3:I9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B3" s="19" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B3" s="16" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H4" t="s">
         <v>499</v>
       </c>
-      <c r="E4" t="s">
+      <c r="I4" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="19" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="16" t="s">
         <v>495</v>
       </c>
       <c r="B5" t="s">
@@ -32532,39 +32566,133 @@
       <c r="C5" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="20" t="s">
+      <c r="D5" t="s">
+        <v>498</v>
+      </c>
+      <c r="E5" t="s">
+        <v>501</v>
+      </c>
+      <c r="F5" t="s">
+        <v>498</v>
+      </c>
+      <c r="G5" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6">
+        <v>98</v>
+      </c>
+      <c r="C6">
+        <v>456914.27</v>
+      </c>
+      <c r="D6">
+        <v>60</v>
+      </c>
+      <c r="E6">
+        <v>185813.51</v>
+      </c>
+      <c r="F6">
+        <v>34</v>
+      </c>
+      <c r="G6">
+        <v>113024.66</v>
+      </c>
+      <c r="H6">
+        <v>192</v>
+      </c>
+      <c r="I6">
+        <v>755752.44000000029</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="21">
-        <v>11</v>
-      </c>
-      <c r="C6" s="21">
-        <v>56016.41</v>
-      </c>
-      <c r="D6" s="21">
-        <v>11</v>
-      </c>
-      <c r="E6" s="21">
-        <v>56016.41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="20" t="s">
+      <c r="B7">
+        <v>74</v>
+      </c>
+      <c r="C7">
+        <v>315265.71000000002</v>
+      </c>
+      <c r="D7">
+        <v>41</v>
+      </c>
+      <c r="E7">
+        <v>182075.99000000002</v>
+      </c>
+      <c r="F7">
+        <v>25</v>
+      </c>
+      <c r="G7">
+        <v>90319.88</v>
+      </c>
+      <c r="H7">
+        <v>140</v>
+      </c>
+      <c r="I7">
+        <v>587661.57999999973</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>66102.430000000008</v>
+      </c>
+      <c r="D8">
+        <v>17</v>
+      </c>
+      <c r="E8">
+        <v>79389.03</v>
+      </c>
+      <c r="F8">
+        <v>6</v>
+      </c>
+      <c r="G8">
+        <v>27976.459999999995</v>
+      </c>
+      <c r="H8">
+        <v>43</v>
+      </c>
+      <c r="I8">
+        <v>173467.91999999995</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="17" t="s">
         <v>496</v>
       </c>
-      <c r="B7" s="21">
-        <v>11</v>
-      </c>
-      <c r="C7" s="21">
-        <v>56016.41</v>
-      </c>
-      <c r="D7" s="21">
-        <v>11</v>
-      </c>
-      <c r="E7" s="21">
-        <v>56016.41</v>
+      <c r="B9">
+        <v>192</v>
+      </c>
+      <c r="C9">
+        <v>838282.40999999992</v>
+      </c>
+      <c r="D9">
+        <v>118</v>
+      </c>
+      <c r="E9">
+        <v>447278.53</v>
+      </c>
+      <c r="F9">
+        <v>65</v>
+      </c>
+      <c r="G9">
+        <v>231321.00000000006</v>
+      </c>
+      <c r="H9">
+        <v>375</v>
+      </c>
+      <c r="I9">
+        <v>1516881.94</v>
       </c>
     </row>
   </sheetData>
